--- a/reports/LeetCode_Daily_Report_2026-08-28.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-28.xlsx
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>73</v>
